--- a/backend/data/financials_by_company/0033.HK.xlsx
+++ b/backend/data/financials_by_company/0033.HK.xlsx
@@ -657,139 +657,145 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44742</v>
       </c>
       <c r="B2" t="n">
-        <v>236610</v>
+        <v>1795700.398517</v>
       </c>
       <c r="C2" t="n">
-        <v>0.165</v>
+        <v>0.062427</v>
       </c>
       <c r="D2" t="n">
-        <v>-16544000</v>
+        <v>21382000</v>
       </c>
       <c r="E2" t="n">
-        <v>1434000</v>
+        <v>28765000</v>
       </c>
       <c r="F2" t="n">
-        <v>1434000</v>
+        <v>28765000</v>
       </c>
       <c r="G2" t="n">
-        <v>-39991000</v>
+        <v>41375000</v>
       </c>
       <c r="H2" t="n">
-        <v>21800000</v>
+        <v>5740000</v>
       </c>
       <c r="I2" t="n">
-        <v>213645000</v>
+        <v>244735000</v>
       </c>
       <c r="J2" t="n">
-        <v>-15110000</v>
+        <v>50147000</v>
       </c>
       <c r="K2" t="n">
-        <v>-36910000</v>
+        <v>44407000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1572000</v>
+        <v>-968000</v>
       </c>
       <c r="M2" t="n">
-        <v>1582000</v>
+        <v>996000</v>
       </c>
       <c r="N2" t="n">
-        <v>10000</v>
+        <v>28000</v>
       </c>
       <c r="O2" t="n">
-        <v>-41188390</v>
+        <v>14405700.398517</v>
       </c>
       <c r="P2" t="n">
-        <v>-39991000</v>
+        <v>41375000</v>
       </c>
       <c r="Q2" t="n">
-        <v>266411000</v>
+        <v>292285000</v>
       </c>
       <c r="R2" t="n">
-        <v>-38365000</v>
+        <v>15656000</v>
       </c>
       <c r="S2" t="n">
-        <v>543040186</v>
+        <v>537245104</v>
       </c>
       <c r="T2" t="n">
-        <v>543040186</v>
+        <v>537245104</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0736</v>
+        <v>0.077</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0736</v>
+        <v>0.077</v>
       </c>
       <c r="W2" t="n">
-        <v>-39991000</v>
+        <v>41375000</v>
       </c>
       <c r="X2" t="n">
-        <v>-39991000</v>
+        <v>41375000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-39991000</v>
+        <v>41375000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-3000</v>
+        <v>674000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-39988000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>40701000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="n">
-        <v>-39988000</v>
+        <v>40701000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1496000</v>
+        <v>2710000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-38492000</v>
+        <v>43411000</v>
       </c>
       <c r="AG2" t="n">
-        <v>861000</v>
+        <v>477000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1455000</v>
+        <v>28751000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1455000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
+        <v>-30497000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>940000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>806000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>-1572000</v>
+        <v>-968000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1582000</v>
+        <v>996000</v>
       </c>
       <c r="AN2" t="n">
-        <v>10000</v>
+        <v>28000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-39700000</v>
+        <v>3276000</v>
       </c>
       <c r="AP2" t="n">
-        <v>52766000</v>
+        <v>47550000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>53416000</v>
+        <v>47750000</v>
       </c>
       <c r="AR2" t="n">
-        <v>13066000</v>
+        <v>50826000</v>
       </c>
       <c r="AS2" t="n">
-        <v>213645000</v>
+        <v>244735000</v>
       </c>
       <c r="AT2" t="n">
-        <v>226711000</v>
+        <v>295561000</v>
       </c>
       <c r="AU2" t="n">
-        <v>226711000</v>
+        <v>295561000</v>
       </c>
     </row>
     <row r="3">
@@ -935,145 +941,139 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45473</v>
       </c>
       <c r="B4" t="n">
-        <v>1795700.398517</v>
+        <v>236610</v>
       </c>
       <c r="C4" t="n">
-        <v>0.062427</v>
+        <v>0.165</v>
       </c>
       <c r="D4" t="n">
-        <v>21382000</v>
+        <v>-16544000</v>
       </c>
       <c r="E4" t="n">
-        <v>28765000</v>
+        <v>1434000</v>
       </c>
       <c r="F4" t="n">
-        <v>28765000</v>
+        <v>1434000</v>
       </c>
       <c r="G4" t="n">
-        <v>41375000</v>
+        <v>-39991000</v>
       </c>
       <c r="H4" t="n">
-        <v>5740000</v>
+        <v>21800000</v>
       </c>
       <c r="I4" t="n">
-        <v>244735000</v>
+        <v>213645000</v>
       </c>
       <c r="J4" t="n">
-        <v>50147000</v>
+        <v>-15110000</v>
       </c>
       <c r="K4" t="n">
-        <v>44407000</v>
+        <v>-36910000</v>
       </c>
       <c r="L4" t="n">
-        <v>-968000</v>
+        <v>-1572000</v>
       </c>
       <c r="M4" t="n">
-        <v>996000</v>
+        <v>1582000</v>
       </c>
       <c r="N4" t="n">
-        <v>28000</v>
+        <v>10000</v>
       </c>
       <c r="O4" t="n">
-        <v>14405700.398517</v>
+        <v>-41188390</v>
       </c>
       <c r="P4" t="n">
-        <v>41375000</v>
+        <v>-39991000</v>
       </c>
       <c r="Q4" t="n">
-        <v>292285000</v>
+        <v>266411000</v>
       </c>
       <c r="R4" t="n">
-        <v>15656000</v>
+        <v>-38365000</v>
       </c>
       <c r="S4" t="n">
-        <v>537245104</v>
+        <v>543040186</v>
       </c>
       <c r="T4" t="n">
-        <v>537245104</v>
+        <v>543040186</v>
       </c>
       <c r="U4" t="n">
-        <v>0.077</v>
+        <v>-0.0736</v>
       </c>
       <c r="V4" t="n">
-        <v>0.077</v>
+        <v>-0.0736</v>
       </c>
       <c r="W4" t="n">
-        <v>41375000</v>
+        <v>-39991000</v>
       </c>
       <c r="X4" t="n">
-        <v>41375000</v>
+        <v>-39991000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>41375000</v>
+        <v>-39991000</v>
       </c>
       <c r="AA4" t="n">
-        <v>674000</v>
+        <v>-3000</v>
       </c>
       <c r="AB4" t="n">
-        <v>40701000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
+        <v>-39988000</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>40701000</v>
+        <v>-39988000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2710000</v>
+        <v>1496000</v>
       </c>
       <c r="AF4" t="n">
-        <v>43411000</v>
+        <v>-38492000</v>
       </c>
       <c r="AG4" t="n">
-        <v>477000</v>
+        <v>861000</v>
       </c>
       <c r="AH4" t="n">
-        <v>28751000</v>
+        <v>1455000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-30497000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>940000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>806000</v>
-      </c>
+        <v>-1455000</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>-968000</v>
+        <v>-1572000</v>
       </c>
       <c r="AM4" t="n">
-        <v>996000</v>
+        <v>1582000</v>
       </c>
       <c r="AN4" t="n">
-        <v>28000</v>
+        <v>10000</v>
       </c>
       <c r="AO4" t="n">
-        <v>3276000</v>
+        <v>-39700000</v>
       </c>
       <c r="AP4" t="n">
-        <v>47550000</v>
+        <v>52766000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>47750000</v>
+        <v>53416000</v>
       </c>
       <c r="AR4" t="n">
-        <v>50826000</v>
+        <v>13066000</v>
       </c>
       <c r="AS4" t="n">
-        <v>244735000</v>
+        <v>213645000</v>
       </c>
       <c r="AT4" t="n">
-        <v>295561000</v>
+        <v>226711000</v>
       </c>
       <c r="AU4" t="n">
-        <v>295561000</v>
+        <v>226711000</v>
       </c>
     </row>
   </sheetData>
@@ -1374,169 +1374,171 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44742</v>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>558245104</v>
+        <v>537245000</v>
       </c>
       <c r="D2" t="n">
-        <v>558245104</v>
+        <v>537245000</v>
       </c>
       <c r="E2" t="n">
-        <v>24535000</v>
+        <v>2181000</v>
       </c>
       <c r="F2" t="n">
-        <v>87476000</v>
+        <v>188336000</v>
       </c>
       <c r="G2" t="n">
-        <v>693411000</v>
+        <v>188336000</v>
       </c>
       <c r="H2" t="n">
-        <v>63241000</v>
+        <v>174087000</v>
       </c>
       <c r="I2" t="n">
-        <v>87476000</v>
+        <v>188336000</v>
       </c>
       <c r="J2" t="n">
-        <v>24535000</v>
+        <v>2181000</v>
       </c>
       <c r="K2" t="n">
-        <v>693411000</v>
+        <v>188336000</v>
       </c>
       <c r="L2" t="n">
-        <v>693411000</v>
+        <v>188336000</v>
       </c>
       <c r="M2" t="n">
-        <v>693441000</v>
+        <v>187576000</v>
       </c>
       <c r="N2" t="n">
-        <v>30000</v>
+        <v>-760000</v>
       </c>
       <c r="O2" t="n">
-        <v>693411000</v>
+        <v>188336000</v>
       </c>
       <c r="P2" t="n">
-        <v>122749000</v>
+        <v>-4116337000</v>
       </c>
       <c r="Q2" t="n">
-        <v>117243000</v>
+        <v>4317787000</v>
       </c>
       <c r="R2" t="n">
-        <v>5582000</v>
+        <v>5372000</v>
       </c>
       <c r="S2" t="n">
-        <v>5582000</v>
+        <v>5372000</v>
       </c>
       <c r="T2" t="n">
-        <v>104652000</v>
+        <v>52063000</v>
       </c>
       <c r="U2" t="n">
-        <v>11563000</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>11563000</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>11563000</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>93089000</v>
+        <v>52063000</v>
       </c>
       <c r="Y2" t="n">
-        <v>12972000</v>
+        <v>2181000</v>
       </c>
       <c r="Z2" t="n">
-        <v>12972000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>2181000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
       <c r="AB2" t="n">
-        <v>59872000</v>
+        <v>25045000</v>
       </c>
       <c r="AC2" t="n">
-        <v>30930000</v>
+        <v>6840000</v>
       </c>
       <c r="AD2" t="n">
         <v>3000</v>
       </c>
       <c r="AE2" t="n">
-        <v>9387000</v>
+        <v>4948000</v>
       </c>
       <c r="AF2" t="n">
-        <v>19552000</v>
+        <v>13254000</v>
       </c>
       <c r="AG2" t="n">
-        <v>798093000</v>
+        <v>239639000</v>
       </c>
       <c r="AH2" t="n">
-        <v>641763000</v>
+        <v>13489000</v>
       </c>
       <c r="AI2" t="n">
-        <v>4584000</v>
+        <v>400000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>605935000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>605935000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>31244000</v>
+        <v>13089000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-9781000</v>
+        <v>-20914000</v>
       </c>
       <c r="AN2" t="n">
-        <v>41025000</v>
+        <v>34003000</v>
       </c>
       <c r="AO2" t="n">
-        <v>20581000</v>
+        <v>13089000</v>
       </c>
       <c r="AP2" t="n">
-        <v>8930000</v>
+        <v>32683000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11514000</v>
+        <v>1320000</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>156330000</v>
+        <v>226150000</v>
       </c>
       <c r="AT2" t="n">
-        <v>658000</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>820000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>95035000</v>
+      </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>10884000</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>10884000</v>
       </c>
       <c r="AX2" t="n">
-        <v>49745000</v>
+        <v>95035000</v>
       </c>
       <c r="AY2" t="n">
-        <v>58119000</v>
+        <v>20060000</v>
       </c>
       <c r="AZ2" t="n">
         <v>-3082000</v>
       </c>
       <c r="BA2" t="n">
-        <v>61201000</v>
+        <v>23142000</v>
       </c>
       <c r="BB2" t="n">
-        <v>47808000</v>
+        <v>99351000</v>
       </c>
       <c r="BC2" t="n">
-        <v>91000</v>
+        <v>160000</v>
       </c>
       <c r="BD2" t="n">
-        <v>47717000</v>
+        <v>99191000</v>
       </c>
       <c r="BE2" t="n">
-        <v>47717000</v>
+        <v>99191000</v>
       </c>
     </row>
     <row r="3">
@@ -1710,171 +1712,169 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45473</v>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>537245000</v>
+        <v>558245104</v>
       </c>
       <c r="D4" t="n">
-        <v>537245000</v>
+        <v>558245104</v>
       </c>
       <c r="E4" t="n">
-        <v>2181000</v>
+        <v>24535000</v>
       </c>
       <c r="F4" t="n">
-        <v>188336000</v>
+        <v>87476000</v>
       </c>
       <c r="G4" t="n">
-        <v>188336000</v>
+        <v>693411000</v>
       </c>
       <c r="H4" t="n">
-        <v>174087000</v>
+        <v>63241000</v>
       </c>
       <c r="I4" t="n">
-        <v>188336000</v>
+        <v>87476000</v>
       </c>
       <c r="J4" t="n">
-        <v>2181000</v>
+        <v>24535000</v>
       </c>
       <c r="K4" t="n">
-        <v>188336000</v>
+        <v>693411000</v>
       </c>
       <c r="L4" t="n">
-        <v>188336000</v>
+        <v>693411000</v>
       </c>
       <c r="M4" t="n">
-        <v>187576000</v>
+        <v>693441000</v>
       </c>
       <c r="N4" t="n">
-        <v>-760000</v>
+        <v>30000</v>
       </c>
       <c r="O4" t="n">
-        <v>188336000</v>
+        <v>693411000</v>
       </c>
       <c r="P4" t="n">
-        <v>-4116337000</v>
+        <v>122749000</v>
       </c>
       <c r="Q4" t="n">
-        <v>4317787000</v>
+        <v>117243000</v>
       </c>
       <c r="R4" t="n">
-        <v>5372000</v>
+        <v>5582000</v>
       </c>
       <c r="S4" t="n">
-        <v>5372000</v>
+        <v>5582000</v>
       </c>
       <c r="T4" t="n">
-        <v>52063000</v>
+        <v>104652000</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>11563000</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>11563000</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>11563000</v>
       </c>
       <c r="X4" t="n">
-        <v>52063000</v>
+        <v>93089000</v>
       </c>
       <c r="Y4" t="n">
-        <v>2181000</v>
+        <v>12972000</v>
       </c>
       <c r="Z4" t="n">
-        <v>2181000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
+        <v>12972000</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>25045000</v>
+        <v>59872000</v>
       </c>
       <c r="AC4" t="n">
-        <v>6840000</v>
+        <v>30930000</v>
       </c>
       <c r="AD4" t="n">
         <v>3000</v>
       </c>
       <c r="AE4" t="n">
-        <v>4948000</v>
+        <v>9387000</v>
       </c>
       <c r="AF4" t="n">
-        <v>13254000</v>
+        <v>19552000</v>
       </c>
       <c r="AG4" t="n">
-        <v>239639000</v>
+        <v>798093000</v>
       </c>
       <c r="AH4" t="n">
-        <v>13489000</v>
+        <v>641763000</v>
       </c>
       <c r="AI4" t="n">
-        <v>400000</v>
+        <v>4584000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
+        <v>605935000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>605935000</v>
+      </c>
       <c r="AL4" t="n">
-        <v>13089000</v>
+        <v>31244000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-20914000</v>
+        <v>-9781000</v>
       </c>
       <c r="AN4" t="n">
-        <v>34003000</v>
+        <v>41025000</v>
       </c>
       <c r="AO4" t="n">
-        <v>13089000</v>
+        <v>20581000</v>
       </c>
       <c r="AP4" t="n">
-        <v>32683000</v>
+        <v>8930000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1320000</v>
+        <v>11514000</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>226150000</v>
+        <v>156330000</v>
       </c>
       <c r="AT4" t="n">
-        <v>820000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>95035000</v>
-      </c>
+        <v>658000</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>10884000</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>10884000</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>95035000</v>
+        <v>49745000</v>
       </c>
       <c r="AY4" t="n">
-        <v>20060000</v>
+        <v>58119000</v>
       </c>
       <c r="AZ4" t="n">
         <v>-3082000</v>
       </c>
       <c r="BA4" t="n">
-        <v>23142000</v>
+        <v>61201000</v>
       </c>
       <c r="BB4" t="n">
-        <v>99351000</v>
+        <v>47808000</v>
       </c>
       <c r="BC4" t="n">
-        <v>160000</v>
+        <v>91000</v>
       </c>
       <c r="BD4" t="n">
-        <v>99191000</v>
+        <v>47717000</v>
       </c>
       <c r="BE4" t="n">
-        <v>99191000</v>
+        <v>47717000</v>
       </c>
     </row>
   </sheetData>
@@ -2110,108 +2110,136 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44742</v>
       </c>
       <c r="B2" t="n">
-        <v>-32823000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+        <v>-109000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1398900000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1255800000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
       <c r="F2" t="n">
-        <v>-13187000</v>
+        <v>-39000</v>
       </c>
       <c r="G2" t="n">
-        <v>47717000</v>
+        <v>99191000</v>
       </c>
       <c r="H2" t="n">
-        <v>89084000</v>
+        <v>248778000</v>
       </c>
       <c r="I2" t="n">
-        <v>117000</v>
+        <v>-1625000</v>
       </c>
       <c r="J2" t="n">
-        <v>-41484000</v>
+        <v>-147962000</v>
       </c>
       <c r="K2" t="n">
-        <v>-15301000</v>
+        <v>-148644000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1582000</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+        <v>-2826000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-143100000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-143100000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-1398900000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1255800000</v>
+      </c>
       <c r="S2" t="n">
-        <v>-6547000</v>
+        <v>752000</v>
       </c>
       <c r="T2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>28000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>763000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>781000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-18000</v>
+      </c>
       <c r="X2" t="n">
-        <v>-6557000</v>
+        <v>-39000</v>
       </c>
       <c r="Y2" t="n">
-        <v>6630000</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-13187000</v>
+        <v>-39000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-19636000</v>
+        <v>-70000</v>
       </c>
       <c r="AB2" t="n">
-        <v>41000</v>
+        <v>-122000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-3123000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>-21302000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-1358000</v>
+      </c>
       <c r="AE2" t="n">
-        <v>167000</v>
+        <v>-57000</v>
       </c>
       <c r="AF2" t="n">
-        <v>12192000</v>
+        <v>23315000</v>
       </c>
       <c r="AG2" t="n">
-        <v>5246000</v>
+        <v>-39569000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-4147000</v>
+        <v>-79237000</v>
       </c>
       <c r="AI2" t="n">
-        <v>9765000</v>
+        <v>-11234000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-26346000</v>
+        <v>86838000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1572000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>968000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
       <c r="AM2" t="n">
-        <v>21800000</v>
+        <v>5740000</v>
       </c>
       <c r="AN2" t="n">
-        <v>21800000</v>
+        <v>5740000</v>
       </c>
       <c r="AO2" t="n">
-        <v>21000</v>
+        <v>-14000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1455000</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-30497000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-38492000</v>
+        <v>43411000</v>
       </c>
     </row>
     <row r="3">
@@ -2342,136 +2370,108 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45473</v>
       </c>
       <c r="B4" t="n">
-        <v>-109000</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-1398900000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1255800000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+        <v>-32823000</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-39000</v>
+        <v>-13187000</v>
       </c>
       <c r="G4" t="n">
-        <v>99191000</v>
+        <v>47717000</v>
       </c>
       <c r="H4" t="n">
-        <v>248778000</v>
+        <v>89084000</v>
       </c>
       <c r="I4" t="n">
-        <v>-1625000</v>
+        <v>117000</v>
       </c>
       <c r="J4" t="n">
-        <v>-147962000</v>
+        <v>-41484000</v>
       </c>
       <c r="K4" t="n">
-        <v>-148644000</v>
+        <v>-15301000</v>
       </c>
       <c r="L4" t="n">
-        <v>-2826000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-143100000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-143100000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-1398900000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1255800000</v>
-      </c>
+        <v>-1582000</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>752000</v>
+        <v>-6547000</v>
       </c>
       <c r="T4" t="n">
-        <v>28000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>763000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>781000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-18000</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>-39000</v>
+        <v>-6557000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>6630000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-39000</v>
+        <v>-13187000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-70000</v>
+        <v>-19636000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-122000</v>
+        <v>41000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-21302000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-1358000</v>
-      </c>
+        <v>-3123000</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>-57000</v>
+        <v>167000</v>
       </c>
       <c r="AF4" t="n">
-        <v>23315000</v>
+        <v>12192000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-39569000</v>
+        <v>5246000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-79237000</v>
+        <v>-4147000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-11234000</v>
+        <v>9765000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>86838000</v>
+        <v>-26346000</v>
       </c>
       <c r="AK4" t="n">
-        <v>968000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
+        <v>1572000</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>5740000</v>
+        <v>21800000</v>
       </c>
       <c r="AN4" t="n">
-        <v>5740000</v>
+        <v>21800000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-14000</v>
+        <v>21000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>-1455000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-30497000</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>43411000</v>
+        <v>-38492000</v>
       </c>
     </row>
   </sheetData>
@@ -3006,162 +3006,162 @@
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
         </is>
       </c>
       <c r="EF1" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Dr. Xiaobin  He', 'age': 63, 'title': 'Chief Economist', 'yearBorn': 1962, 'fiscalYear': 2024, 'totalPay': 110000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yongxiang  Pan', 'age': 37, 'title': 'Executive Chairman', 'yearBorn': 1988, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kai Weng  Leong', 'age': 38, 'title': 'Company Secretary', 'yearBorn': 1987, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Dr. Xiaobin  He', 'age': 63, 'title': 'Chief Economist', 'yearBorn': 1962, 'fiscalYear': 2024, 'totalPay': 110000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yongxiang  Pan', 'age': 37, 'title': 'Executive Chairman', 'yearBorn': 1988, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hing Tok  Poon', 'age': 38, 'title': 'Executive Director', 'yearBorn': 1987, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kai Weng  Leong', 'age': 38, 'title': 'Company Secretary', 'yearBorn': 1987, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -3319,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.258</v>
+        <v>-0.174</v>
       </c>
       <c r="AD2" t="n">
         <v>302800</v>
@@ -3358,7 +3358,7 @@
         <v>0.39</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="AQ2" t="n">
         <v>3021.563</v>
@@ -3373,7 +3373,7 @@
         <v>0.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.4136</v>
+        <v>0.402025</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -3449,10 +3449,10 @@
         <v>-28.473</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0.35483873</v>
+        <v>-0.48717946</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="BU2" t="n">
         <v>3.662501</v>
@@ -3567,117 +3567,117 @@
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
+          <t>INTL GENIUS</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>0.395 - 0.415</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>0.01000002</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0.025641078</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>0.39 - 1.05</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.61904764</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>-48.717945</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1740738281</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>1740738281</v>
+      </c>
+      <c r="DN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.0020250082</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.0050370204</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>Amber Hill Financial Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="DX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1195435800000</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
           <t>International Genius Company</t>
         </is>
       </c>
-      <c r="DA2" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>-0.013599992</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>-0.032881994</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>Amber Hill Financial Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>INTL GENIUS</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DO2" t="n">
+      <c r="EE2" t="n">
         <v>1759219682</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>1195435800000</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>0.395 - 0.415</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.01000002</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>0.025641078</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>0.39 - 1.28</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.6875</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-35.48387</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1740738281</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>1740738281</v>
-      </c>
-      <c r="EE2" t="b">
-        <v>0</v>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
